--- a/experience.xlsx
+++ b/experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Archtria\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88E85D0-9CC9-4B06-99A5-4DC2ADB7B22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B270665-4371-4C89-85D8-E79E9BA6B829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사업 명단" sheetId="2" r:id="rId1"/>
@@ -305,10 +305,6 @@
     <t>(재)이노베이션 아카데미</t>
   </si>
   <si>
-    <t xml:space="preserve">「2024년 스타기업 육성사업」 원포인트 지원사업
-중장기 성장전략 컨설팅 용역 </t>
-  </si>
-  <si>
     <t>주식회사 제이솔루션</t>
   </si>
   <si>
@@ -447,13 +443,6 @@
     <t>산업DX 지원플랫폼고도화를 위한 글로벌 동향 보고서 작성/ 업로드및DX분야컨설팅</t>
   </si>
   <si>
-    <t>성과확산형 국제협력 기술개발사업-아세안 지역에 적합한 AI기반 선별과제 시스템의 현지 실증 및 시장화 기술 개발</t>
-  </si>
-  <si>
-    <t>국토교통부
-국토교통과학기술진흥원</t>
-  </si>
-  <si>
     <t>2023년 신성장동력 기술사업화 지원사업</t>
   </si>
   <si>
@@ -683,6 +672,486 @@
   </si>
   <si>
     <t>국가첨단전략산업 소부장 투자지원금 컨택센터 운영</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스타기업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>육성사업」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원포인트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지원사업 중장기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성장전략</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>컨설팅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>용역</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성과확산형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국제협력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기술개발사업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아세안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지역에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적합한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선별과제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시스템의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>현지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실증</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시장화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기술</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>국토교통부 국토교통과학기술진흥원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -693,7 +1162,7 @@
     <numFmt numFmtId="176" formatCode="yyyy&quot;. &quot;mm&quot;. &quot;dd"/>
     <numFmt numFmtId="177" formatCode="[$₩]#,##0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -713,6 +1182,21 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -735,7 +1219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -752,32 +1236,188 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="26">
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FFD4D4D4"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FFD4D4D4"/>
-        </horizontal>
-      </border>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="[$₩]#,##0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -828,14 +1468,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD4D7F0"/>
-          <bgColor rgb="FFD4D7F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
           <bgColor rgb="FFF6F8F9"/>
         </patternFill>
@@ -846,6 +1478,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD4D7F0"/>
+          <bgColor rgb="FFD4D7F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -949,32 +1589,54 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFD4D4D4"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFD4D4D4"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="4">
     <tableStyle name="4. 용역 분류-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="13"/>
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="secondRowStripe" dxfId="14"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="25"/>
+      <tableStyleElement type="headerRow" dxfId="24"/>
+      <tableStyleElement type="firstRowStripe" dxfId="23"/>
+      <tableStyleElement type="secondRowStripe" dxfId="22"/>
     </tableStyle>
     <tableStyle name="3. 인력 명단-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="9"/>
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="secondRowStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="21"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="firstRowStripe" dxfId="19"/>
+      <tableStyleElement type="secondRowStripe" dxfId="18"/>
     </tableStyle>
     <tableStyle name="2. 사업 명단-style" pivot="0" count="5" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
     <tableStyle name="6. 참여율-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="firstRowStripe" dxfId="10"/>
+      <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -988,23 +1650,19 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="사업_수행_실적" displayName="사업_수행_실적" ref="A1:I128" totalsRowCount="1">
   <autoFilter ref="A1:I127" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="사업번호"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="분야"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="영역"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="사업(용역)명"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="발주처"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="사업시작"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="사업종료"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="사업 기간(연월)"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="금액" totalsRowFunction="custom">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="사업번호" totalsRowDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="분야" totalsRowDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="영역" totalsRowDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="사업(용역)명" totalsRowDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="발주처" totalsRowDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="사업시작" totalsRowDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="사업종료" totalsRowDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="사업 기간(연월)" totalsRowDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="금액" totalsRowFunction="custom" totalsRowDxfId="0">
       <totalsRowFormula>SUM(사업_수행_실적[금액])</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -1214,7 +1872,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I128"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
@@ -1226,7 +1884,7 @@
     <col min="9" max="9" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="22.5" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
@@ -1255,7 +1913,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="22.5" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>10</v>
@@ -1283,7 +1941,7 @@
         <v>38800000</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="22.5" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>15</v>
@@ -1311,7 +1969,7 @@
         <v>55800000</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="22.5" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>4</v>
@@ -1339,7 +1997,7 @@
         <v>74400000</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="22.5" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -1367,7 +2025,7 @@
         <v>33600000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="22.5" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>6</v>
@@ -1395,7 +2053,7 @@
         <v>9500000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="22.5" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>6</v>
@@ -1423,7 +2081,7 @@
         <v>19800000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="22.5" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -1451,7 +2109,7 @@
         <v>60000000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="22.5" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>2</v>
@@ -1479,7 +2137,7 @@
         <v>60000000</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="22.5" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -1507,7 +2165,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="22.5" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>2</v>
@@ -1535,7 +2193,7 @@
         <v>5500000</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="22.5" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>4</v>
@@ -1563,7 +2221,7 @@
         <v>4980000</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="22.5" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>2</v>
@@ -1591,7 +2249,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="22.5" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>14</v>
@@ -1619,7 +2277,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="22.5" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
         <v>15</v>
@@ -1647,7 +2305,7 @@
         <v>70000000</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="22.5" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>8</v>
@@ -1675,7 +2333,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="22.5" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>16</v>
@@ -1703,7 +2361,7 @@
         <v>17000000</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="22.5" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>14</v>
@@ -1731,7 +2389,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="22.5" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>4</v>
@@ -1759,7 +2417,7 @@
         <v>9850000</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="22.5" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>12</v>
@@ -1787,7 +2445,7 @@
         <v>22000000</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="22.5" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
         <v>6</v>
@@ -1815,7 +2473,7 @@
         <v>19500000</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="22.5" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>14</v>
@@ -1843,7 +2501,7 @@
         <v>31800000</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="22.5" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
         <v>6</v>
@@ -1871,7 +2529,7 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="22.5" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
         <v>10</v>
@@ -1899,7 +2557,7 @@
         <v>49700000</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="22.5" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
         <v>2</v>
@@ -1927,7 +2585,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="22.5" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
         <v>10</v>
@@ -1955,7 +2613,7 @@
         <v>38000000</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="22.5" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
         <v>10</v>
@@ -1983,7 +2641,7 @@
         <v>59400000</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="22.5" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
         <v>2</v>
@@ -2011,7 +2669,7 @@
         <v>30000000</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="22.5" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
         <v>6</v>
@@ -2039,7 +2697,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="22.5" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
         <v>4</v>
@@ -2067,7 +2725,7 @@
         <v>1650000</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="22.5" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
         <v>2</v>
@@ -2095,7 +2753,7 @@
         <v>44015840</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="22.5" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
         <v>8</v>
@@ -2123,7 +2781,7 @@
         <v>11550000.000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="22.5" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>6</v>
@@ -2151,7 +2809,7 @@
         <v>16500000</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="22.5" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1" t="s">
         <v>10</v>
@@ -2179,7 +2837,7 @@
         <v>22000000</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="22.5" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1" t="s">
         <v>14</v>
@@ -2207,7 +2865,7 @@
         <v>19800000</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="22.5" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
         <v>14</v>
@@ -2235,7 +2893,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="22.5" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
         <v>10</v>
@@ -2263,7 +2921,7 @@
         <v>12000000</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="22.5" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
         <v>10</v>
@@ -2291,7 +2949,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="22.5" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
         <v>14</v>
@@ -2319,7 +2977,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="22.5" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1" t="s">
         <v>14</v>
@@ -2347,7 +3005,7 @@
         <v>19800000</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="22.5" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
         <v>4</v>
@@ -2375,7 +3033,7 @@
         <v>19800000</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="27">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
         <v>14</v>
@@ -2383,11 +3041,11 @@
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="F42" s="4">
         <v>45597</v>
@@ -2403,7 +3061,7 @@
         <v>18150000</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="22.5" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1" t="s">
         <v>6</v>
@@ -2412,10 +3070,10 @@
         <v>5</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F43" s="4">
         <v>45597</v>
@@ -2431,7 +3089,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="22.5" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1" t="s">
         <v>4</v>
@@ -2440,10 +3098,10 @@
         <v>5</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="F44" s="4">
         <v>45576</v>
@@ -2459,7 +3117,7 @@
         <v>80000000</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="22.5" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
         <v>4</v>
@@ -2468,10 +3126,10 @@
         <v>5</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F45" s="4">
         <v>45562</v>
@@ -2487,7 +3145,7 @@
         <v>84000000</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="22.5" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
         <v>12</v>
@@ -2496,10 +3154,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="F46" s="4">
         <v>45561</v>
@@ -2515,7 +3173,7 @@
         <v>34300000</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="22.5" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
         <v>2</v>
@@ -2524,7 +3182,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>48</v>
@@ -2543,7 +3201,7 @@
         <v>74630000</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="22.5" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>14</v>
@@ -2552,10 +3210,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="F48" s="4">
         <v>45520</v>
@@ -2571,7 +3229,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" ht="22.5" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="1" t="s">
         <v>14</v>
@@ -2580,7 +3238,7 @@
         <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>44</v>
@@ -2599,7 +3257,7 @@
         <v>21800000</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" ht="22.5" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1" t="s">
         <v>14</v>
@@ -2608,10 +3266,10 @@
         <v>13</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="F50" s="4">
         <v>45457</v>
@@ -2627,7 +3285,7 @@
         <v>88000000</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" ht="22.5" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
         <v>10</v>
@@ -2636,7 +3294,7 @@
         <v>5</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>70</v>
@@ -2655,7 +3313,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="22.5" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1" t="s">
         <v>14</v>
@@ -2664,7 +3322,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>42</v>
@@ -2683,7 +3341,7 @@
         <v>4950000</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" ht="22.5" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1" t="s">
         <v>14</v>
@@ -2692,7 +3350,7 @@
         <v>7</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>42</v>
@@ -2711,7 +3369,7 @@
         <v>98000000</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" ht="22.5" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1" t="s">
         <v>4</v>
@@ -2720,10 +3378,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="F54" s="4">
         <v>45383</v>
@@ -2739,7 +3397,7 @@
         <v>141600000</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" ht="22.5" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1" t="s">
         <v>2</v>
@@ -2748,10 +3406,10 @@
         <v>5</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="F55" s="4">
         <v>45383</v>
@@ -2767,7 +3425,7 @@
         <v>18500000</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" ht="22.5" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1" t="s">
         <v>16</v>
@@ -2776,7 +3434,7 @@
         <v>3</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>42</v>
@@ -2795,7 +3453,7 @@
         <v>3900000</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" ht="22.5" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1" t="s">
         <v>12</v>
@@ -2804,10 +3462,10 @@
         <v>5</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="F57" s="4">
         <v>45383</v>
@@ -2823,7 +3481,7 @@
         <v>21000000</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" ht="22.5" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1" t="s">
         <v>4</v>
@@ -2832,10 +3490,10 @@
         <v>11</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="F58" s="4">
         <v>45355</v>
@@ -2851,7 +3509,7 @@
         <v>66000000</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" ht="22.5" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
         <v>10</v>
@@ -2860,7 +3518,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>25</v>
@@ -2879,7 +3537,7 @@
         <v>48400000</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" ht="22.5" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1" t="s">
         <v>8</v>
@@ -2888,10 +3546,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="F60" s="4">
         <v>45352</v>
@@ -2907,7 +3565,7 @@
         <v>18400000</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" ht="22.5" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1" t="s">
         <v>14</v>
@@ -2916,10 +3574,10 @@
         <v>13</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F61" s="4">
         <v>45323</v>
@@ -2935,7 +3593,7 @@
         <v>19700000</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" ht="22.5" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="1" t="s">
         <v>14</v>
@@ -2944,7 +3602,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>42</v>
@@ -2963,7 +3621,7 @@
         <v>18150000</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" ht="22.5" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="1" t="s">
         <v>6</v>
@@ -2972,10 +3630,10 @@
         <v>5</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="F63" s="4">
         <v>45292</v>
@@ -2991,7 +3649,7 @@
         <v>7700000</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" ht="22.5" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="1" t="s">
         <v>14</v>
@@ -3000,7 +3658,7 @@
         <v>7</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>44</v>
@@ -3019,7 +3677,7 @@
         <v>21500000</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" ht="22.5" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="1" t="s">
         <v>14</v>
@@ -3028,7 +3686,7 @@
         <v>13</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>44</v>
@@ -3047,7 +3705,7 @@
         <v>21800000</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" ht="22.5" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="1" t="s">
         <v>2</v>
@@ -3056,7 +3714,7 @@
         <v>11</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>70</v>
@@ -3075,7 +3733,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" ht="22.5" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
         <v>4</v>
@@ -3084,10 +3742,10 @@
         <v>5</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="F67" s="4">
         <v>45231</v>
@@ -3103,7 +3761,7 @@
         <v>8550000</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" ht="22.5" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1" t="s">
         <v>4</v>
@@ -3112,10 +3770,10 @@
         <v>7</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="F68" s="4">
         <v>45231</v>
@@ -3131,7 +3789,7 @@
         <v>96800000</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" ht="22.5" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1" t="s">
         <v>2</v>
@@ -3140,10 +3798,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="F69" s="4">
         <v>45231</v>
@@ -3159,7 +3817,7 @@
         <v>20125000</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" ht="22.5" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1" t="s">
         <v>10</v>
@@ -3168,10 +3826,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="F70" s="4">
         <v>45231</v>
@@ -3187,7 +3845,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" ht="22.5" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1" t="s">
         <v>4</v>
@@ -3196,7 +3854,7 @@
         <v>11</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>70</v>
@@ -3215,7 +3873,7 @@
         <v>28600000</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" ht="22.5" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="1" t="s">
         <v>2</v>
@@ -3223,11 +3881,11 @@
       <c r="C72" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>137</v>
+      <c r="D72" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="F72" s="4">
         <v>45108</v>
@@ -3243,7 +3901,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" ht="22.5" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="1" t="s">
         <v>14</v>
@@ -3252,10 +3910,10 @@
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F73" s="4">
         <v>45108</v>
@@ -3271,7 +3929,7 @@
         <v>15500000</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" ht="22.5" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1" t="s">
         <v>6</v>
@@ -3280,7 +3938,7 @@
         <v>5</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>70</v>
@@ -3299,7 +3957,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" ht="22.5" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="1" t="s">
         <v>4</v>
@@ -3308,10 +3966,10 @@
         <v>5</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F75" s="4">
         <v>45108</v>
@@ -3327,7 +3985,7 @@
         <v>4950000</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" ht="22.5" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="1" t="s">
         <v>4</v>
@@ -3336,10 +3994,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F76" s="4">
         <v>45108</v>
@@ -3355,7 +4013,7 @@
         <v>33000000</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" ht="22.5" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1" t="s">
         <v>2</v>
@@ -3364,10 +4022,10 @@
         <v>7</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F77" s="4">
         <v>45078</v>
@@ -3383,7 +4041,7 @@
         <v>73800000</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" ht="22.5" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="1" t="s">
         <v>4</v>
@@ -3392,10 +4050,10 @@
         <v>7</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F78" s="4">
         <v>45078</v>
@@ -3411,7 +4069,7 @@
         <v>4750000</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" ht="22.5" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1" t="s">
         <v>14</v>
@@ -3420,10 +4078,10 @@
         <v>5</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F79" s="4">
         <v>45078</v>
@@ -3439,7 +4097,7 @@
         <v>7350000</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" ht="22.5" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1" t="s">
         <v>4</v>
@@ -3448,7 +4106,7 @@
         <v>3</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>27</v>
@@ -3467,7 +4125,7 @@
         <v>77000000</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" ht="22.5" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1" t="s">
         <v>14</v>
@@ -3476,10 +4134,10 @@
         <v>7</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F81" s="4">
         <v>45047</v>
@@ -3495,7 +4153,7 @@
         <v>92890000</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" ht="22.5" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1" t="s">
         <v>12</v>
@@ -3504,10 +4162,10 @@
         <v>5</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F82" s="4">
         <v>44958</v>
@@ -3523,7 +4181,7 @@
         <v>21000000</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="22.5" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1" t="s">
         <v>14</v>
@@ -3532,10 +4190,10 @@
         <v>7</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F83" s="4">
         <v>44927</v>
@@ -3551,7 +4209,7 @@
         <v>4750000</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" ht="22.5" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1" t="s">
         <v>14</v>
@@ -3560,10 +4218,10 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F84" s="4">
         <v>44927</v>
@@ -3579,7 +4237,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" ht="22.5" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1" t="s">
         <v>6</v>
@@ -3588,10 +4246,10 @@
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F85" s="4">
         <v>44927</v>
@@ -3607,7 +4265,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" ht="22.5" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1" t="s">
         <v>14</v>
@@ -3616,10 +4274,10 @@
         <v>5</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F86" s="4">
         <v>44927</v>
@@ -3635,7 +4293,7 @@
         <v>4400000</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" ht="22.5" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1" t="s">
         <v>10</v>
@@ -3644,7 +4302,7 @@
         <v>3</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>25</v>
@@ -3663,7 +4321,7 @@
         <v>76000000</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" ht="22.5" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
         <v>14</v>
@@ -3672,10 +4330,10 @@
         <v>7</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F88" s="4">
         <v>44896</v>
@@ -3691,7 +4349,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" ht="22.5" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
         <v>14</v>
@@ -3700,10 +4358,10 @@
         <v>5</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F89" s="4">
         <v>44866</v>
@@ -3719,7 +4377,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" ht="22.5" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1" t="s">
         <v>4</v>
@@ -3728,10 +4386,10 @@
         <v>5</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F90" s="4">
         <v>44866</v>
@@ -3747,7 +4405,7 @@
         <v>64500000</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" ht="22.5" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1" t="s">
         <v>8</v>
@@ -3756,10 +4414,10 @@
         <v>5</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F91" s="4">
         <v>44866</v>
@@ -3775,7 +4433,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" ht="22.5" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1" t="s">
         <v>14</v>
@@ -3784,10 +4442,10 @@
         <v>5</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F92" s="4">
         <v>44866</v>
@@ -3803,7 +4461,7 @@
         <v>84700000</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" ht="22.5" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1" t="s">
         <v>4</v>
@@ -3812,7 +4470,7 @@
         <v>5</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>70</v>
@@ -3831,7 +4489,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" ht="22.5" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1" t="s">
         <v>14</v>
@@ -3840,10 +4498,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F94" s="4">
         <v>44866</v>
@@ -3859,7 +4517,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" ht="22.5" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1" t="s">
         <v>14</v>
@@ -3868,10 +4526,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F95" s="4">
         <v>44805</v>
@@ -3887,7 +4545,7 @@
         <v>16000000</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" ht="22.5" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1" t="s">
         <v>2</v>
@@ -3896,10 +4554,10 @@
         <v>7</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F96" s="4">
         <v>44774</v>
@@ -3915,7 +4573,7 @@
         <v>63700000</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" ht="22.5" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1" t="s">
         <v>4</v>
@@ -3924,10 +4582,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F97" s="4">
         <v>44774</v>
@@ -3943,7 +4601,7 @@
         <v>19800000</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" ht="22.5" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1" t="s">
         <v>2</v>
@@ -3952,10 +4610,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F98" s="4">
         <v>44774</v>
@@ -3971,7 +4629,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="22.5" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1" t="s">
         <v>14</v>
@@ -3980,10 +4638,10 @@
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F99" s="4">
         <v>44743</v>
@@ -3999,7 +4657,7 @@
         <v>15000000</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="22.5" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1" t="s">
         <v>4</v>
@@ -4008,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F100" s="4">
         <v>44682</v>
@@ -4027,7 +4685,7 @@
         <v>60000000</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" ht="22.5" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1" t="s">
         <v>4</v>
@@ -4036,10 +4694,10 @@
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F101" s="4">
         <v>44652</v>
@@ -4055,7 +4713,7 @@
         <v>120000000</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="22.5" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1" t="s">
         <v>14</v>
@@ -4064,10 +4722,10 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F102" s="4">
         <v>44652</v>
@@ -4083,7 +4741,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="22.5" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1" t="s">
         <v>14</v>
@@ -4092,10 +4750,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F103" s="4">
         <v>44593</v>
@@ -4111,7 +4769,7 @@
         <v>19800000</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" ht="22.5" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1" t="s">
         <v>2</v>
@@ -4120,10 +4778,10 @@
         <v>7</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F104" s="4">
         <v>44562</v>
@@ -4139,7 +4797,7 @@
         <v>8550000</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="22.5" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1" t="s">
         <v>14</v>
@@ -4148,10 +4806,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F105" s="4">
         <v>44562</v>
@@ -4167,7 +4825,7 @@
         <v>17850000</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="22.5" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1" t="s">
         <v>16</v>
@@ -4176,10 +4834,10 @@
         <v>7</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F106" s="4">
         <v>44409</v>
@@ -4195,7 +4853,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" ht="22.5" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1" t="s">
         <v>4</v>
@@ -4204,7 +4862,7 @@
         <v>11</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>70</v>
@@ -4223,7 +4881,7 @@
         <v>78500000</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" ht="22.5" customHeight="1">
       <c r="A108" s="1"/>
       <c r="B108" s="1" t="s">
         <v>16</v>
@@ -4232,10 +4890,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F108" s="4">
         <v>44409</v>
@@ -4251,7 +4909,7 @@
         <v>165167000</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" ht="22.5" customHeight="1">
       <c r="A109" s="1"/>
       <c r="B109" s="1" t="s">
         <v>4</v>
@@ -4260,10 +4918,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F109" s="4">
         <v>44409</v>
@@ -4279,7 +4937,7 @@
         <v>19600000</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" ht="22.5" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1" t="s">
         <v>2</v>
@@ -4288,10 +4946,10 @@
         <v>11</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F110" s="4">
         <v>44378</v>
@@ -4307,7 +4965,7 @@
         <v>107250000</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" ht="22.5" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="1" t="s">
         <v>4</v>
@@ -4316,7 +4974,7 @@
         <v>7</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>31</v>
@@ -4335,7 +4993,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" ht="22.5" customHeight="1">
       <c r="A112" s="1"/>
       <c r="B112" s="1" t="s">
         <v>4</v>
@@ -4344,7 +5002,7 @@
         <v>11</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>31</v>
@@ -4363,7 +5021,7 @@
         <v>30000000</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" ht="22.5" customHeight="1">
       <c r="A113" s="1"/>
       <c r="B113" s="1" t="s">
         <v>6</v>
@@ -4372,7 +5030,7 @@
         <v>13</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>27</v>
@@ -4391,7 +5049,7 @@
         <v>49470000</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" ht="22.5" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1" t="s">
         <v>14</v>
@@ -4400,10 +5058,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F114" s="4">
         <v>44044</v>
@@ -4419,7 +5077,7 @@
         <v>6000000</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" ht="22.5" customHeight="1">
       <c r="A115" s="1"/>
       <c r="B115" s="1" t="s">
         <v>4</v>
@@ -4428,7 +5086,7 @@
         <v>3</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>31</v>
@@ -4447,7 +5105,7 @@
         <v>21450000</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" ht="22.5" customHeight="1">
       <c r="A116" s="1"/>
       <c r="B116" s="1" t="s">
         <v>15</v>
@@ -4456,7 +5114,7 @@
         <v>3</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>48</v>
@@ -4475,7 +5133,7 @@
         <v>144921000</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" ht="22.5" customHeight="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1" t="s">
         <v>4</v>
@@ -4484,7 +5142,7 @@
         <v>3</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>27</v>
@@ -4503,7 +5161,7 @@
         <v>77600000</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" ht="22.5" customHeight="1">
       <c r="A118" s="1"/>
       <c r="B118" s="1" t="s">
         <v>14</v>
@@ -4512,7 +5170,7 @@
         <v>7</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>27</v>
@@ -4531,7 +5189,7 @@
         <v>77000000</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" ht="22.5" customHeight="1">
       <c r="A119" s="1"/>
       <c r="B119" s="1" t="s">
         <v>2</v>
@@ -4540,10 +5198,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F119" s="4">
         <v>43770</v>
@@ -4559,7 +5217,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" ht="22.5" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="1" t="s">
         <v>6</v>
@@ -4568,7 +5226,7 @@
         <v>13</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>27</v>
@@ -4581,7 +5239,7 @@
       </c>
       <c r="I120" s="3"/>
     </row>
-    <row r="121" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" ht="22.5" customHeight="1">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4595,7 +5253,7 @@
       </c>
       <c r="I121" s="3"/>
     </row>
-    <row r="122" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" ht="22.5" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4608,7 +5266,7 @@
       </c>
       <c r="I122" s="3"/>
     </row>
-    <row r="123" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" ht="22.5" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4622,7 +5280,7 @@
       </c>
       <c r="I123" s="3"/>
     </row>
-    <row r="124" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" ht="22.5" customHeight="1">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4636,7 +5294,7 @@
       </c>
       <c r="I124" s="3"/>
     </row>
-    <row r="125" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" ht="22.5" customHeight="1">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4650,7 +5308,7 @@
       </c>
       <c r="I125" s="3"/>
     </row>
-    <row r="126" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" ht="22.5" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4664,7 +5322,7 @@
       </c>
       <c r="I126" s="3"/>
     </row>
-    <row r="127" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" ht="22.5" customHeight="1">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4678,7 +5336,7 @@
       </c>
       <c r="I127" s="3"/>
     </row>
-    <row r="128" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" ht="22.5" customHeight="1">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
